--- a/ci-cd-merge-resolver/repoCollector/datasets/curator.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/curator.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,84 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>770aa411d00f97ce6040f2b4182d6f0fe744262d</t>
+  </si>
+  <si>
+    <t>b58cfd068dbe4771f83365124693049b6051f63e</t>
+  </si>
+  <si>
+    <t>144977f8bc94115fac53163f81310aff0d50c78d</t>
+  </si>
+  <si>
+    <t>d7a65ad5e90c26cb487fe864146b01277dd8cc1a</t>
+  </si>
+  <si>
+    <t>62f428c0456113628bf714bec756c1e13270b80f</t>
+  </si>
+  <si>
+    <t>e2aef818200b42bd289f5b1fb84ce45220cc99d4</t>
+  </si>
+  <si>
+    <t>540cd28a33bccc6423765851631a02dcd974b89f</t>
+  </si>
+  <si>
+    <t>f645190739cb8c26a19fba1d469faef8966db418</t>
+  </si>
+  <si>
+    <t>2342578f424230ee9dd0abfd47f0042f9c422343</t>
+  </si>
+  <si>
+    <t>da48ef388f6153e66d251121854bb0faae77a3ec</t>
+  </si>
+  <si>
+    <t>e683264798e73187f86f7f9dbb07a476f3f1384b</t>
+  </si>
+  <si>
+    <t>d3bccce4e4a03591ca33c2f8ae56a1abf6cbc9b6</t>
+  </si>
+  <si>
+    <t>905b062b370c3cff399f3f726a6d74ab44d7618e</t>
+  </si>
+  <si>
+    <t>d8798c21de10926cecd2ffc11f1ed7ce695c330a</t>
+  </si>
+  <si>
+    <t>e9bfb4353ae75dd5aa369ae4aa76b9d8cadb7e50</t>
+  </si>
+  <si>
+    <t>e6ed99965b6df91607b2505a3784780e51fa8c53</t>
+  </si>
+  <si>
+    <t>60d24c2c982ef185ac10d08d01a7eca8f6d57e61</t>
+  </si>
+  <si>
+    <t>0a0a1e7d8beac27cd07dd0f445e55e9c6646e10c</t>
+  </si>
+  <si>
+    <t>d034aeaedf43a22f25db76fbe257caef53d40897</t>
+  </si>
+  <si>
+    <t>dd20f1dbed3879372483d7e8f7eb05d920707168</t>
+  </si>
+  <si>
+    <t>0e23fbac1be51df269f1b396af03980f8a614cab</t>
+  </si>
+  <si>
+    <t>7d44baee3d87890b67fc4900f204bb5111368079</t>
+  </si>
+  <si>
+    <t>337b9d929c6e027719044559de65468c044c4251</t>
+  </si>
+  <si>
+    <t>1826b66d72f6e543a57aaf5f3acc3cd9ca6e965d</t>
+  </si>
+  <si>
+    <t>e7d57eccfc756efb2cac83edf25da9d57f740553</t>
+  </si>
+  <si>
+    <t>b3939acd47b6198930812236678ceae6f6f6a7af</t>
+  </si>
+  <si>
     <t>caf2a9d81a333154a0d36fcea1a624d4e00df3e1</t>
   </si>
   <si>
@@ -51,6 +129,24 @@
   </si>
   <si>
     <t>05f6a56730a956b5a977a11e05aa875fe862dedf</t>
+  </si>
+  <si>
+    <t>666b175228d7e642d1b0bbf049119a628501900e</t>
+  </si>
+  <si>
+    <t>74013456da1260f9155a72fa651d5d6fa449d984</t>
+  </si>
+  <si>
+    <t>c6f7aeb39957158fad0207614583f867729e7770</t>
+  </si>
+  <si>
+    <t>da7f18c618eb51e6aaaff7b10f79240cefaf0183</t>
+  </si>
+  <si>
+    <t>e3fec5bc7fcd1091c3f07317039d1d5ed20f2d66</t>
+  </si>
+  <si>
+    <t>00ffe77951a88ea12c60a506a9beff1ae78de300</t>
   </si>
 </sst>
 </file>
@@ -95,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,7 +237,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -156,10 +252,362 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>9.598999977111816</v>
+        <v>1.871000051498413</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>1.3350000381469727</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>1.7359999418258667</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>1.7280000448226929</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G6" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>2.4030001163482666</v>
+      </c>
+      <c r="J6" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>1.812999963760376</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>1.3140000104904175</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>2.234999895095825</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>1.5540000200271606</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>38.12299728393555</v>
+      </c>
+      <c r="J11" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>36.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>43.09400177001953</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>36.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>45.196998596191406</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
